--- a/開發系統表分析表格.xlsx
+++ b/開發系統表分析表格.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_code\AntiGravity_code\TCM-Meridian\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5421480E-FF8E-4C9C-9083-F26D79AEA82D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2442B160-B26F-4045-9DE5-7A0AC1CF8C59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="55">
   <si>
     <t>prompt_record_update</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -598,6 +598,10 @@
   </si>
   <si>
     <t>病歷修改 diff 過程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>診間對話逐字稿</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1105,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64655AA0-732C-4848-9798-7F7FE16ECA47}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="42.3984375" style="14" bestFit="1" customWidth="1"/>
@@ -1335,8 +1339,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="17">
-      <c r="A9" s="9" t="s">
-        <v>28</v>
+      <c r="A9" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="B9" s="16" t="s">
         <v>2</v>
@@ -1347,50 +1351,50 @@
       <c r="D9" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>28</v>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="17"/>
+      <c r="I9" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="17">
       <c r="A10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17">
+      <c r="A11" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="17">
-      <c r="A11" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="17"/>
+      <c r="B11" s="16" t="s">
+        <v>2</v>
+      </c>
       <c r="C11" s="15" t="s">
         <v>2</v>
       </c>
@@ -1399,21 +1403,23 @@
       </c>
       <c r="E11" s="15"/>
       <c r="F11" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="I11" s="9" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="17">
       <c r="A12" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="16" t="s">
-        <v>48</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B12" s="17"/>
       <c r="C12" s="15" t="s">
         <v>2</v>
       </c>
@@ -1422,36 +1428,59 @@
       </c>
       <c r="E12" s="15"/>
       <c r="F12" s="15" t="s">
-        <v>2</v>
+        <v>46</v>
       </c>
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
       <c r="I12" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="17">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="E13" s="16"/>
-      <c r="F13" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="16" t="s">
-        <v>2</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="17"/>
       <c r="H13" s="17"/>
       <c r="I13" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17">
+      <c r="A14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="H14" s="17"/>
+      <c r="I14" s="7" t="s">
         <v>53</v>
       </c>
     </row>
